--- a/CodeSystem-chul-location-cs.xlsx
+++ b/CodeSystem-chul-location-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/CodeSystem-chul-location-cs.xlsx
+++ b/CodeSystem-chul-location-cs.xlsx
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>Case Sensitive</t>
